--- a/data/trans_orig/P04B1_2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>418433</t>
+          <t>416831</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>464583</t>
+          <t>464041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>517598</t>
+          <t>518642</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>583442</t>
+          <t>579993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>949730</t>
+          <t>948745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1030466</t>
+          <t>1028748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169829</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215979</t>
+          <t>217581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141247</t>
+          <t>144696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207091</t>
+          <t>206047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>328634</t>
+          <t>330352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>409370</t>
+          <t>410355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>721063</t>
+          <t>723971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>997013</t>
+          <t>1017253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>559436</t>
+          <t>559752</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>609130</t>
+          <t>612491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1308855</t>
+          <t>1308800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1656029</t>
+          <t>1661486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193899</t>
+          <t>173659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469849</t>
+          <t>466941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348740</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>398434</t>
+          <t>398118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>492752</t>
+          <t>487295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>839926</t>
+          <t>839981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>493078</t>
+          <t>494775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>542555</t>
+          <t>546188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>649111</t>
+          <t>650225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>820199</t>
+          <t>832035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1173709</t>
+          <t>1170274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1369005</t>
+          <t>1392813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161961</t>
+          <t>158328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>211438</t>
+          <t>209741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112511</t>
+          <t>100675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283599</t>
+          <t>282485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268221</t>
+          <t>244413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>463517</t>
+          <t>466952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>491588</t>
+          <t>492397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>553976</t>
+          <t>559136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>586755</t>
+          <t>586665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>721057</t>
+          <t>716056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1099642</t>
+          <t>1101264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1258881</t>
+          <t>1248638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>370807</t>
+          <t>365647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>433195</t>
+          <t>432386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373145</t>
+          <t>378146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507447</t>
+          <t>507537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>760105</t>
+          <t>770348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>919344</t>
+          <t>917722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2213853</t>
+          <t>2218726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2551761</t>
+          <t>2597903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2369045</t>
+          <t>2370128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2680116</t>
+          <t>2693560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4623740</t>
+          <t>4631446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5098632</t>
+          <t>5102104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>902861</t>
+          <t>856719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1240769</t>
+          <t>1235896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1029355</t>
+          <t>1015911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1340426</t>
+          <t>1339343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2065461</t>
+          <t>2061989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2540353</t>
+          <t>2532647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>441642</t>
+          <t>470127</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>416831</t>
+          <t>443602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>464041</t>
+          <t>494703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>541969</t>
+          <t>529368</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>518642</t>
+          <t>507695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>579993</t>
+          <t>548689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>983611</t>
+          <t>999495</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>948745</t>
+          <t>967421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1028748</t>
+          <t>1034307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>192770</t>
+          <t>219501</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170371</t>
+          <t>194925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217581</t>
+          <t>246026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>182720</t>
+          <t>204134</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144696</t>
+          <t>184813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206047</t>
+          <t>225807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>375489</t>
+          <t>423635</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>330352</t>
+          <t>388823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>410355</t>
+          <t>455709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>724689</t>
+          <t>733502</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>724689</t>
+          <t>733502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>724689</t>
+          <t>733502</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1359100</t>
+          <t>1423130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1359100</t>
+          <t>1423130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1359100</t>
+          <t>1423130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>832435</t>
+          <t>626461</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>723971</t>
+          <t>587681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1017253</t>
+          <t>658894</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>584403</t>
+          <t>647931</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>559752</t>
+          <t>620251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>612491</t>
+          <t>677914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1416837</t>
+          <t>1274392</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1308800</t>
+          <t>1230820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1661486</t>
+          <t>1322604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>358477</t>
+          <t>420285</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173659</t>
+          <t>387852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>466941</t>
+          <t>459065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>373467</t>
+          <t>421867</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345379</t>
+          <t>391884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>398118</t>
+          <t>449547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>731944</t>
+          <t>842151</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487295</t>
+          <t>793939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>839981</t>
+          <t>885723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1190912</t>
+          <t>1046746</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1190912</t>
+          <t>1046746</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1190912</t>
+          <t>1046746</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957870</t>
+          <t>1069798</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957870</t>
+          <t>1069798</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957870</t>
+          <t>1069798</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148781</t>
+          <t>2116543</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148781</t>
+          <t>2116543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148781</t>
+          <t>2116543</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>520101</t>
+          <t>593255</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>494775</t>
+          <t>564145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>546188</t>
+          <t>623438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>722188</t>
+          <t>556456</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>650225</t>
+          <t>533900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>832035</t>
+          <t>580726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1242288</t>
+          <t>1149711</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1170274</t>
+          <t>1109715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1392813</t>
+          <t>1183417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>184415</t>
+          <t>208640</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158328</t>
+          <t>178457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209741</t>
+          <t>237750</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>210522</t>
+          <t>255096</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100675</t>
+          <t>230826</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>282485</t>
+          <t>277652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>394938</t>
+          <t>463736</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244413</t>
+          <t>430030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>466952</t>
+          <t>503732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>524307</t>
+          <t>531294</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>492397</t>
+          <t>497452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>559136</t>
+          <t>565689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>629807</t>
+          <t>584148</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>586665</t>
+          <t>552039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>716056</t>
+          <t>611419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1154114</t>
+          <t>1115442</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1101264</t>
+          <t>1069838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1248638</t>
+          <t>1161876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>400476</t>
+          <t>455309</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365647</t>
+          <t>420914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>432386</t>
+          <t>489151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>464395</t>
+          <t>534147</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378146</t>
+          <t>506876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507537</t>
+          <t>566256</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>864872</t>
+          <t>989456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>770348</t>
+          <t>943022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>917722</t>
+          <t>1035060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924783</t>
+          <t>986603</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924783</t>
+          <t>986603</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924783</t>
+          <t>986603</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018986</t>
+          <t>2104898</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018986</t>
+          <t>2104898</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018986</t>
+          <t>2104898</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2318485</t>
+          <t>2221137</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2218726</t>
+          <t>2159459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2597903</t>
+          <t>2279291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2478366</t>
+          <t>2317903</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2370128</t>
+          <t>2264233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2693560</t>
+          <t>2373117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4796851</t>
+          <t>4539040</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4631446</t>
+          <t>4459440</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5102104</t>
+          <t>4619412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1136137</t>
+          <t>1303734</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>856719</t>
+          <t>1245580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1235896</t>
+          <t>1365412</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1231105</t>
+          <t>1415244</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1015911</t>
+          <t>1360030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1339343</t>
+          <t>1468914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2367242</t>
+          <t>2718978</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2061989</t>
+          <t>2638606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2532647</t>
+          <t>2798578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454622</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3709471</t>
+          <t>3733147</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7164093</t>
+          <t>7258018</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
